--- a/public/AgencyData/agency.xlsx
+++ b/public/AgencyData/agency.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rafiramadhan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrdfy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC751E3-E3B8-144C-8037-199972E46BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E36B1B0-3348-4C84-BEA6-84010E2D23FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -52,16 +51,25 @@
     <t>PIC</t>
   </si>
   <si>
-    <t>Agensi test</t>
-  </si>
-  <si>
-    <t>agnesi@gmail.com</t>
-  </si>
-  <si>
-    <t>test alamat</t>
+    <t>test alamat2</t>
   </si>
   <si>
     <t>Tina</t>
+  </si>
+  <si>
+    <t>agnesiana@gmail.com</t>
+  </si>
+  <si>
+    <t>Agensi tests coba saja</t>
+  </si>
+  <si>
+    <t>Agensi testing</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>alamat jekardag</t>
   </si>
 </sst>
 </file>
@@ -75,10 +83,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,14 +106,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -408,10 +418,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -431,25 +446,51 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
       </c>
       <c r="E2">
         <v>12345678910</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>8323384738</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{C3834498-564F-4C14-9760-FB05F84B1AB3}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{8CA070F1-D49C-414B-A216-70560140E72C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>